--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-e0e166b4-0f77-478d-9062-de0034d98ce0.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/StructureDefinition-e0e166b4-0f77-478d-9062-de0034d98ce0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7544" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7544" uniqueCount="705">
   <si>
     <t>Property</t>
   </si>
@@ -1195,6 +1195,13 @@
     <t>resultType</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/ConsentManagement/CodeSystem/ResultType"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
   </si>
   <si>
@@ -1235,6 +1242,13 @@
   </si>
   <si>
     <t>templateType</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://fhir.de/ConsentManagement/CodeSystem/TemplateType"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
@@ -11364,7 +11378,7 @@
         <v>76</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>76</v>
+        <v>378</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>76</v>
@@ -11383,7 +11397,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>76</v>
@@ -11427,7 +11441,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>341</v>
@@ -11536,7 +11550,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>343</v>
@@ -11647,7 +11661,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>345</v>
@@ -11760,7 +11774,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>347</v>
@@ -11869,7 +11883,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>349</v>
@@ -11980,7 +11994,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>351</v>
@@ -12093,7 +12107,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>353</v>
@@ -12204,7 +12218,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>355</v>
@@ -12315,7 +12329,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>357</v>
@@ -12426,7 +12440,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>359</v>
@@ -12539,7 +12553,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>361</v>
@@ -12652,13 +12666,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>327</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>76</v>
@@ -12698,7 +12712,7 @@
         <v>76</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>76</v>
@@ -12717,7 +12731,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>76</v>
@@ -12761,7 +12775,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>341</v>
@@ -12870,7 +12884,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>343</v>
@@ -12981,7 +12995,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>345</v>
@@ -13094,7 +13108,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>347</v>
@@ -13203,7 +13217,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>349</v>
@@ -13314,7 +13328,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>351</v>
@@ -13427,7 +13441,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>353</v>
@@ -13538,7 +13552,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>355</v>
@@ -13649,7 +13663,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>357</v>
@@ -13760,7 +13774,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>359</v>
@@ -13873,7 +13887,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>361</v>
@@ -13986,10 +14000,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14012,16 +14026,16 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14071,7 +14085,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14086,21 +14100,21 @@
         <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14206,10 +14220,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14317,10 +14331,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14346,13 +14360,13 @@
         <v>101</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14402,7 +14416,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14411,7 +14425,7 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>99</v>
@@ -14428,10 +14442,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14457,13 +14471,13 @@
         <v>128</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14492,10 +14506,10 @@
         <v>144</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>76</v>
@@ -14513,7 +14527,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14539,10 +14553,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14568,13 +14582,13 @@
         <v>278</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14624,7 +14638,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14650,10 +14664,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14759,10 +14773,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14870,10 +14884,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14899,16 +14913,16 @@
         <v>162</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -14936,10 +14950,10 @@
         <v>222</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -14957,7 +14971,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -14975,7 +14989,7 @@
         <v>76</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>76</v>
@@ -14983,10 +14997,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15012,16 +15026,16 @@
         <v>296</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -15049,10 +15063,10 @@
         <v>144</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>76</v>
@@ -15070,7 +15084,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -15088,7 +15102,7 @@
         <v>76</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>76</v>
@@ -15096,10 +15110,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15125,16 +15139,16 @@
         <v>128</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -15147,7 +15161,7 @@
         <v>76</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>76</v>
@@ -15183,7 +15197,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15201,7 +15215,7 @@
         <v>76</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>76</v>
@@ -15209,10 +15223,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15238,13 +15252,13 @@
         <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15258,7 +15272,7 @@
         <v>76</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>76</v>
@@ -15294,7 +15308,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15312,7 +15326,7 @@
         <v>76</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>76</v>
@@ -15320,10 +15334,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15346,13 +15360,13 @@
         <v>88</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15403,7 +15417,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15421,7 +15435,7 @@
         <v>76</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>76</v>
@@ -15429,10 +15443,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15455,16 +15469,16 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15514,7 +15528,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15532,7 +15546,7 @@
         <v>76</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>76</v>
@@ -15540,10 +15554,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15569,13 +15583,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15625,7 +15639,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15651,10 +15665,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15677,16 +15691,16 @@
         <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15736,7 +15750,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15751,25 +15765,25 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -15788,16 +15802,16 @@
         <v>88</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15847,7 +15861,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -15862,25 +15876,25 @@
         <v>99</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -15899,13 +15913,13 @@
         <v>88</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15956,7 +15970,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -15971,21 +15985,21 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16008,16 +16022,16 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16067,7 +16081,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -16085,7 +16099,7 @@
         <v>76</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>76</v>
@@ -16093,10 +16107,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16202,10 +16216,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16313,10 +16327,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16342,13 +16356,13 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16398,7 +16412,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16407,7 +16421,7 @@
         <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>99</v>
@@ -16424,10 +16438,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16453,13 +16467,13 @@
         <v>128</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16488,10 +16502,10 @@
         <v>144</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>76</v>
@@ -16509,7 +16523,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16535,10 +16549,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16564,13 +16578,13 @@
         <v>278</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16620,7 +16634,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -16646,10 +16660,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16675,13 +16689,13 @@
         <v>101</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16731,7 +16745,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -16757,10 +16771,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16783,13 +16797,13 @@
         <v>76</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -16840,7 +16854,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>77</v>
@@ -16866,10 +16880,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16975,10 +16989,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17086,14 +17100,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17115,10 +17129,10 @@
         <v>107</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>110</v>
@@ -17173,7 +17187,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -17199,10 +17213,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17228,10 +17242,10 @@
         <v>128</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17282,7 +17296,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -17291,7 +17305,7 @@
         <v>87</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>99</v>
@@ -17308,10 +17322,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17337,13 +17351,13 @@
         <v>128</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17393,7 +17407,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>77</v>
@@ -17402,7 +17416,7 @@
         <v>87</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>99</v>
@@ -17419,10 +17433,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17448,16 +17462,16 @@
         <v>296</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -17485,10 +17499,10 @@
         <v>144</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -17506,7 +17520,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>77</v>
@@ -17515,7 +17529,7 @@
         <v>87</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -17532,10 +17546,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17641,10 +17655,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17750,13 +17764,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>76</v>
@@ -17778,7 +17792,7 @@
         <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>191</v>
@@ -17861,10 +17875,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17974,10 +17988,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18087,10 +18101,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18113,13 +18127,13 @@
         <v>88</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18170,7 +18184,7 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
@@ -18196,10 +18210,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18305,10 +18319,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18416,14 +18430,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18445,10 +18459,10 @@
         <v>107</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>110</v>
@@ -18503,7 +18517,7 @@
         <v>76</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
@@ -18529,10 +18543,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18558,10 +18572,10 @@
         <v>259</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18612,7 +18626,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18638,10 +18652,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18664,13 +18678,13 @@
         <v>76</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -18721,7 +18735,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -18747,10 +18761,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18773,13 +18787,13 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -18830,7 +18844,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>77</v>
@@ -18856,10 +18870,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18882,13 +18896,13 @@
         <v>88</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -18939,7 +18953,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>77</v>
@@ -18965,10 +18979,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19074,10 +19088,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19185,14 +19199,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19214,10 +19228,10 @@
         <v>107</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N151" t="s" s="2">
         <v>110</v>
@@ -19272,7 +19286,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>77</v>
@@ -19298,10 +19312,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19327,10 +19341,10 @@
         <v>162</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -19360,10 +19374,10 @@
         <v>222</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>76</v>
@@ -19381,7 +19395,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>77</v>
@@ -19407,10 +19421,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19433,13 +19447,13 @@
         <v>88</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -19490,7 +19504,7 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>77</v>
@@ -19516,10 +19530,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19625,10 +19639,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19736,10 +19750,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19762,16 +19776,16 @@
         <v>88</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19821,7 +19835,7 @@
         <v>76</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
@@ -19830,7 +19844,7 @@
         <v>87</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>99</v>
@@ -19839,7 +19853,7 @@
         <v>76</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>76</v>
@@ -19847,10 +19861,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19873,23 +19887,23 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q157" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="R157" t="s" s="2">
         <v>76</v>
@@ -19934,7 +19948,7 @@
         <v>76</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>77</v>
@@ -19943,7 +19957,7 @@
         <v>87</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>99</v>
@@ -19952,7 +19966,7 @@
         <v>76</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>76</v>
@@ -19960,10 +19974,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19986,13 +20000,13 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -20000,7 +20014,7 @@
         <v>76</v>
       </c>
       <c r="Q158" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="R158" t="s" s="2">
         <v>76</v>
@@ -20045,7 +20059,7 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>77</v>
@@ -20071,10 +20085,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20180,10 +20194,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20291,14 +20305,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -20320,10 +20334,10 @@
         <v>107</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>110</v>
@@ -20378,7 +20392,7 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>77</v>
@@ -20404,10 +20418,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20433,10 +20447,10 @@
         <v>296</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20466,10 +20480,10 @@
         <v>144</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>76</v>
@@ -20487,7 +20501,7 @@
         <v>76</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20513,10 +20527,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20539,13 +20553,13 @@
         <v>76</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -20596,7 +20610,7 @@
         <v>76</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>87</v>
@@ -20622,10 +20636,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20651,20 +20665,20 @@
         <v>296</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q164" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="R164" t="s" s="2">
         <v>76</v>
@@ -20688,10 +20702,10 @@
         <v>152</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>76</v>
@@ -20709,7 +20723,7 @@
         <v>76</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>77</v>
@@ -20735,10 +20749,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20764,13 +20778,13 @@
         <v>140</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -20820,7 +20834,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>77</v>
@@ -20846,10 +20860,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20875,13 +20889,13 @@
         <v>140</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -20910,10 +20924,10 @@
         <v>144</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>76</v>
@@ -20931,7 +20945,7 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -20957,10 +20971,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20986,13 +21000,13 @@
         <v>140</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -21021,10 +21035,10 @@
         <v>144</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>76</v>
@@ -21042,7 +21056,7 @@
         <v>76</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>77</v>
@@ -21068,10 +21082,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21097,13 +21111,13 @@
         <v>296</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -21132,10 +21146,10 @@
         <v>152</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>76</v>
@@ -21153,7 +21167,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>77</v>
@@ -21179,10 +21193,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21205,16 +21219,16 @@
         <v>88</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21264,7 +21278,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>77</v>
@@ -21290,10 +21304,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21316,13 +21330,13 @@
         <v>88</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -21330,7 +21344,7 @@
         <v>76</v>
       </c>
       <c r="Q170" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="R170" t="s" s="2">
         <v>76</v>
@@ -21375,7 +21389,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>77</v>
@@ -21401,10 +21415,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21510,10 +21524,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21621,14 +21635,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -21650,10 +21664,10 @@
         <v>107</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>110</v>
@@ -21708,7 +21722,7 @@
         <v>76</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>77</v>
@@ -21734,10 +21748,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21763,10 +21777,10 @@
         <v>162</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -21796,10 +21810,10 @@
         <v>222</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>76</v>
@@ -21817,7 +21831,7 @@
         <v>76</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>87</v>
@@ -21843,10 +21857,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21869,13 +21883,13 @@
         <v>88</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -21926,7 +21940,7 @@
         <v>76</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>87</v>
@@ -21952,10 +21966,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21978,13 +21992,13 @@
         <v>76</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22035,7 +22049,7 @@
         <v>76</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>77</v>
@@ -22061,10 +22075,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22170,10 +22184,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22281,14 +22295,14 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -22310,10 +22324,10 @@
         <v>107</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>110</v>
@@ -22368,7 +22382,7 @@
         <v>76</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>77</v>
@@ -22394,10 +22408,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22423,10 +22437,10 @@
         <v>162</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -22456,10 +22470,10 @@
         <v>222</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>76</v>
@@ -22477,7 +22491,7 @@
         <v>76</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>77</v>
@@ -22503,10 +22517,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22529,13 +22543,13 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -22586,7 +22600,7 @@
         <v>76</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>77</v>
@@ -22612,10 +22626,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -22721,10 +22735,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -22832,10 +22846,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -22858,16 +22872,16 @@
         <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
@@ -22917,7 +22931,7 @@
         <v>76</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>77</v>
@@ -22926,7 +22940,7 @@
         <v>87</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>99</v>
@@ -22935,7 +22949,7 @@
         <v>76</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>76</v>
@@ -22943,10 +22957,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -22969,23 +22983,23 @@
         <v>88</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q185" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="R185" t="s" s="2">
         <v>76</v>
@@ -23030,7 +23044,7 @@
         <v>76</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>77</v>
@@ -23039,7 +23053,7 @@
         <v>87</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>99</v>
@@ -23048,7 +23062,7 @@
         <v>76</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>76</v>
@@ -23056,10 +23070,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23082,13 +23096,13 @@
         <v>76</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -23096,7 +23110,7 @@
         <v>76</v>
       </c>
       <c r="Q186" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="R186" t="s" s="2">
         <v>76</v>
@@ -23141,7 +23155,7 @@
         <v>76</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>77</v>
@@ -23167,10 +23181,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23276,10 +23290,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23387,14 +23401,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
@@ -23416,10 +23430,10 @@
         <v>107</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N189" t="s" s="2">
         <v>110</v>
@@ -23474,7 +23488,7 @@
         <v>76</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>77</v>
@@ -23500,10 +23514,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -23529,10 +23543,10 @@
         <v>296</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -23562,10 +23576,10 @@
         <v>144</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>76</v>
@@ -23583,7 +23597,7 @@
         <v>76</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>87</v>
@@ -23609,10 +23623,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -23635,13 +23649,13 @@
         <v>76</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -23692,7 +23706,7 @@
         <v>76</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>87</v>
@@ -23718,10 +23732,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -23747,20 +23761,20 @@
         <v>296</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q192" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="R192" t="s" s="2">
         <v>76</v>
@@ -23784,10 +23798,10 @@
         <v>152</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>76</v>
@@ -23805,7 +23819,7 @@
         <v>76</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>77</v>
@@ -23831,10 +23845,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -23860,13 +23874,13 @@
         <v>140</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -23916,7 +23930,7 @@
         <v>76</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>77</v>
@@ -23942,10 +23956,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -23971,13 +23985,13 @@
         <v>140</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -24006,10 +24020,10 @@
         <v>144</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>76</v>
@@ -24027,7 +24041,7 @@
         <v>76</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>77</v>
@@ -24053,10 +24067,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24082,13 +24096,13 @@
         <v>140</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -24117,10 +24131,10 @@
         <v>144</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>76</v>
@@ -24138,7 +24152,7 @@
         <v>76</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>77</v>
@@ -24164,10 +24178,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24193,13 +24207,13 @@
         <v>296</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -24229,7 +24243,7 @@
       </c>
       <c r="Y196" s="2"/>
       <c r="Z196" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>76</v>
@@ -24247,7 +24261,7 @@
         <v>76</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>77</v>
@@ -24273,10 +24287,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -24382,10 +24396,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -24493,10 +24507,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -24606,10 +24620,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -24715,10 +24729,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -24826,10 +24840,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -24939,10 +24953,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -25050,10 +25064,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -25161,10 +25175,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -25272,10 +25286,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -25385,10 +25399,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -25498,10 +25512,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -25524,16 +25538,16 @@
         <v>88</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -25583,7 +25597,7 @@
         <v>76</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>77</v>
@@ -25609,10 +25623,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25635,13 +25649,13 @@
         <v>88</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -25649,7 +25663,7 @@
         <v>76</v>
       </c>
       <c r="Q209" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="R209" t="s" s="2">
         <v>76</v>
@@ -25694,7 +25708,7 @@
         <v>76</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25720,10 +25734,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25829,10 +25843,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -25940,14 +25954,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -25969,10 +25983,10 @@
         <v>107</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>110</v>
@@ -26027,7 +26041,7 @@
         <v>76</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>77</v>
@@ -26053,10 +26067,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -26082,10 +26096,10 @@
         <v>162</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -26115,10 +26129,10 @@
         <v>222</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>76</v>
@@ -26136,7 +26150,7 @@
         <v>76</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>87</v>
@@ -26162,10 +26176,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -26188,13 +26202,13 @@
         <v>88</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -26245,7 +26259,7 @@
         <v>76</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>87</v>
@@ -26271,10 +26285,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -26300,10 +26314,10 @@
         <v>76</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -26354,7 +26368,7 @@
         <v>76</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>77</v>
